--- a/Data_Booking/Booking Supra 27-06-2026.xlsx
+++ b/Data_Booking/Booking Supra 27-06-2026.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chinhqt\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDA27DA9-42A3-4BD4-A4FB-6335A18C5C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0EC10A-036B-4FAE-AD3E-177C6B1AB202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{64C42A11-1259-4439-ACF0-73989F91B5B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet3!$A$1:$AB$115</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="501">
   <si>
     <t/>
   </si>
@@ -2164,8 +2167,8 @@
       <c r="G2" s="2">
         <v>240</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>0</v>
+      <c r="H2" s="4">
+        <v>7</v>
       </c>
       <c r="I2" s="4">
         <v>92.897800000000018</v>
@@ -2238,8 +2241,8 @@
       <c r="G3" s="2">
         <v>240</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>0</v>
+      <c r="H3" s="4">
+        <v>10</v>
       </c>
       <c r="I3" s="4">
         <v>87.068999999999988</v>
@@ -2312,8 +2315,8 @@
       <c r="G4" s="2">
         <v>204</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>0</v>
+      <c r="H4" s="4">
+        <v>7</v>
       </c>
       <c r="I4" s="4">
         <v>94.2012</v>
@@ -2386,8 +2389,8 @@
       <c r="G5" s="2">
         <v>60</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>0</v>
+      <c r="H5" s="4">
+        <v>2</v>
       </c>
       <c r="I5" s="4">
         <v>6.3</v>
@@ -2460,8 +2463,8 @@
       <c r="G6" s="2">
         <v>150</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>0</v>
+      <c r="H6" s="4">
+        <v>6</v>
       </c>
       <c r="I6" s="4">
         <v>25.087200000000003</v>
@@ -2534,8 +2537,8 @@
       <c r="G7" s="2">
         <v>54</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>0</v>
+      <c r="H7" s="4">
+        <v>2</v>
       </c>
       <c r="I7" s="4">
         <v>5.7</v>
@@ -2608,8 +2611,8 @@
       <c r="G8" s="2">
         <v>156</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>0</v>
+      <c r="H8" s="4">
+        <v>7</v>
       </c>
       <c r="I8" s="4">
         <v>16.692</v>
@@ -2682,8 +2685,8 @@
       <c r="G9" s="2">
         <v>42</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>0</v>
+      <c r="H9" s="4">
+        <v>2</v>
       </c>
       <c r="I9" s="4">
         <v>4.6840000000000002</v>
@@ -2756,8 +2759,8 @@
       <c r="G10" s="2">
         <v>174</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>0</v>
+      <c r="H10" s="4">
+        <v>7</v>
       </c>
       <c r="I10" s="4">
         <v>24.523199999999999</v>
@@ -2830,8 +2833,8 @@
       <c r="G11" s="2">
         <v>30</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>0</v>
+      <c r="H11" s="4">
+        <v>1</v>
       </c>
       <c r="I11" s="4">
         <v>2.1450000000000005</v>
@@ -2904,8 +2907,8 @@
       <c r="G12" s="2">
         <v>108</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>0</v>
+      <c r="H12" s="4">
+        <v>4</v>
       </c>
       <c r="I12" s="4">
         <v>10.8192</v>
@@ -2978,8 +2981,8 @@
       <c r="G13" s="2">
         <v>234</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>0</v>
+      <c r="H13" s="4">
+        <v>9</v>
       </c>
       <c r="I13" s="4">
         <v>81.659199999999998</v>
@@ -3052,8 +3055,8 @@
       <c r="G14" s="2">
         <v>120</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>0</v>
+      <c r="H14" s="4">
+        <v>5</v>
       </c>
       <c r="I14" s="4">
         <v>14.152200000000001</v>
@@ -3126,8 +3129,8 @@
       <c r="G15" s="2">
         <v>48</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>0</v>
+      <c r="H15" s="4">
+        <v>2</v>
       </c>
       <c r="I15" s="4">
         <v>17.952000000000002</v>
@@ -3200,8 +3203,8 @@
       <c r="G16" s="2">
         <v>108</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>0</v>
+      <c r="H16" s="4">
+        <v>4</v>
       </c>
       <c r="I16" s="4">
         <v>12.379200000000001</v>
@@ -3274,8 +3277,8 @@
       <c r="G17" s="2">
         <v>24</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>0</v>
+      <c r="H17" s="4">
+        <v>1</v>
       </c>
       <c r="I17" s="4">
         <v>3.3528000000000002</v>
@@ -3348,8 +3351,8 @@
       <c r="G18" s="2">
         <v>90</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>0</v>
+      <c r="H18" s="4">
+        <v>4</v>
       </c>
       <c r="I18" s="4">
         <v>10.808800000000002</v>
@@ -3422,8 +3425,8 @@
       <c r="G19" s="2">
         <v>264</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>0</v>
+      <c r="H19" s="4">
+        <v>11</v>
       </c>
       <c r="I19" s="4">
         <v>106.13640000000001</v>
@@ -3496,8 +3499,8 @@
       <c r="G20" s="2">
         <v>258</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>0</v>
+      <c r="H20" s="4">
+        <v>10</v>
       </c>
       <c r="I20" s="4">
         <v>73.580799999999996</v>
@@ -3570,8 +3573,8 @@
       <c r="G21" s="2">
         <v>198</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>0</v>
+      <c r="H21" s="4">
+        <v>8</v>
       </c>
       <c r="I21" s="4">
         <v>78.585599999999999</v>
@@ -3644,8 +3647,8 @@
       <c r="G22" s="2">
         <v>18</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>0</v>
+      <c r="H22" s="4">
+        <v>1</v>
       </c>
       <c r="I22" s="4">
         <v>2.1780000000000004</v>
@@ -3718,8 +3721,8 @@
       <c r="G23" s="2">
         <v>144</v>
       </c>
-      <c r="H23" s="4" t="s">
-        <v>0</v>
+      <c r="H23" s="4">
+        <v>5</v>
       </c>
       <c r="I23" s="4">
         <v>19.926000000000002</v>
@@ -3792,8 +3795,8 @@
       <c r="G24" s="2">
         <v>168</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>0</v>
+      <c r="H24" s="4">
+        <v>6</v>
       </c>
       <c r="I24" s="4">
         <v>67.030799999999999</v>
@@ -3866,8 +3869,8 @@
       <c r="G25" s="2">
         <v>186</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>0</v>
+      <c r="H25" s="4">
+        <v>7</v>
       </c>
       <c r="I25" s="4">
         <v>31.684200000000004</v>
@@ -3940,8 +3943,8 @@
       <c r="G26" s="2">
         <v>60</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>0</v>
+      <c r="H26" s="4">
+        <v>2</v>
       </c>
       <c r="I26" s="4">
         <v>6.3</v>
@@ -4014,8 +4017,8 @@
       <c r="G27" s="2">
         <v>72</v>
       </c>
-      <c r="H27" s="4" t="s">
-        <v>0</v>
+      <c r="H27" s="4">
+        <v>3</v>
       </c>
       <c r="I27" s="4">
         <v>25.987200000000001</v>
@@ -4088,8 +4091,8 @@
       <c r="G28" s="2">
         <v>84</v>
       </c>
-      <c r="H28" s="4" t="s">
-        <v>0</v>
+      <c r="H28" s="4">
+        <v>3</v>
       </c>
       <c r="I28" s="4">
         <v>9</v>
@@ -4162,8 +4165,8 @@
       <c r="G29" s="2">
         <v>72</v>
       </c>
-      <c r="H29" s="4" t="s">
-        <v>0</v>
+      <c r="H29" s="4">
+        <v>3</v>
       </c>
       <c r="I29" s="4">
         <v>8.5380000000000003</v>
@@ -4236,8 +4239,8 @@
       <c r="G30" s="2">
         <v>120</v>
       </c>
-      <c r="H30" s="4" t="s">
-        <v>0</v>
+      <c r="H30" s="4">
+        <v>5</v>
       </c>
       <c r="I30" s="4">
         <v>25.836000000000002</v>
@@ -4310,8 +4313,8 @@
       <c r="G31" s="2">
         <v>36</v>
       </c>
-      <c r="H31" s="4" t="s">
-        <v>0</v>
+      <c r="H31" s="4">
+        <v>2</v>
       </c>
       <c r="I31" s="4">
         <v>10.56</v>
@@ -4384,8 +4387,8 @@
       <c r="G32" s="2">
         <v>48</v>
       </c>
-      <c r="H32" s="4" t="s">
-        <v>0</v>
+      <c r="H32" s="4">
+        <v>2</v>
       </c>
       <c r="I32" s="4">
         <v>5.4779999999999998</v>
@@ -4458,8 +4461,8 @@
       <c r="G33" s="2">
         <v>60</v>
       </c>
-      <c r="H33" s="4" t="s">
-        <v>0</v>
+      <c r="H33" s="4">
+        <v>2</v>
       </c>
       <c r="I33" s="4">
         <v>5.1450000000000005</v>
@@ -4532,8 +4535,8 @@
       <c r="G34" s="2">
         <v>84</v>
       </c>
-      <c r="H34" s="4" t="s">
-        <v>0</v>
+      <c r="H34" s="4">
+        <v>3</v>
       </c>
       <c r="I34" s="4">
         <v>8.8463999999999992</v>
@@ -4606,8 +4609,8 @@
       <c r="G35" s="2">
         <v>48</v>
       </c>
-      <c r="H35" s="4" t="s">
-        <v>0</v>
+      <c r="H35" s="4">
+        <v>2</v>
       </c>
       <c r="I35" s="4">
         <v>6.0528000000000004</v>
@@ -4680,8 +4683,8 @@
       <c r="G36" s="2">
         <v>276</v>
       </c>
-      <c r="H36" s="4" t="s">
-        <v>0</v>
+      <c r="H36" s="4">
+        <v>10</v>
       </c>
       <c r="I36" s="4">
         <v>98.252800000000008</v>
@@ -4754,8 +4757,8 @@
       <c r="G37" s="2">
         <v>264</v>
       </c>
-      <c r="H37" s="4" t="s">
-        <v>0</v>
+      <c r="H37" s="4">
+        <v>7</v>
       </c>
       <c r="I37" s="4">
         <v>64.116</v>
@@ -4828,8 +4831,8 @@
       <c r="G38" s="2">
         <v>150</v>
       </c>
-      <c r="H38" s="4" t="s">
-        <v>0</v>
+      <c r="H38" s="4">
+        <v>6</v>
       </c>
       <c r="I38" s="4">
         <v>17.16</v>
@@ -4902,8 +4905,8 @@
       <c r="G39" s="2">
         <v>78</v>
       </c>
-      <c r="H39" s="4" t="s">
-        <v>0</v>
+      <c r="H39" s="4">
+        <v>3</v>
       </c>
       <c r="I39" s="4">
         <v>9.75</v>
@@ -4976,8 +4979,8 @@
       <c r="G40" s="2">
         <v>324</v>
       </c>
-      <c r="H40" s="4" t="s">
-        <v>0</v>
+      <c r="H40" s="4">
+        <v>13</v>
       </c>
       <c r="I40" s="4">
         <v>36.4452</v>
@@ -5050,8 +5053,8 @@
       <c r="G41" s="2">
         <v>84</v>
       </c>
-      <c r="H41" s="4" t="s">
-        <v>0</v>
+      <c r="H41" s="4">
+        <v>3</v>
       </c>
       <c r="I41" s="4">
         <v>14.976000000000001</v>
@@ -5124,8 +5127,8 @@
       <c r="G42" s="2">
         <v>102</v>
       </c>
-      <c r="H42" s="4" t="s">
-        <v>0</v>
+      <c r="H42" s="4">
+        <v>4</v>
       </c>
       <c r="I42" s="4">
         <v>17.6952</v>
@@ -5198,8 +5201,8 @@
       <c r="G43" s="2">
         <v>348</v>
       </c>
-      <c r="H43" s="4" t="s">
-        <v>0</v>
+      <c r="H43" s="4">
+        <v>14</v>
       </c>
       <c r="I43" s="4">
         <v>120.7608</v>
@@ -5272,8 +5275,8 @@
       <c r="G44" s="2">
         <v>72</v>
       </c>
-      <c r="H44" s="4" t="s">
-        <v>0</v>
+      <c r="H44" s="4">
+        <v>2</v>
       </c>
       <c r="I44" s="4">
         <v>41.100000000000009</v>
@@ -5346,8 +5349,8 @@
       <c r="G45" s="2">
         <v>72</v>
       </c>
-      <c r="H45" s="4" t="s">
-        <v>0</v>
+      <c r="H45" s="4">
+        <v>3</v>
       </c>
       <c r="I45" s="4">
         <v>40.975200000000001</v>
@@ -5420,8 +5423,8 @@
       <c r="G46" s="2">
         <v>198</v>
       </c>
-      <c r="H46" s="4" t="s">
-        <v>0</v>
+      <c r="H46" s="4">
+        <v>7</v>
       </c>
       <c r="I46" s="4">
         <v>27.376000000000005</v>
@@ -5494,8 +5497,8 @@
       <c r="G47" s="2">
         <v>90</v>
       </c>
-      <c r="H47" s="4" t="s">
-        <v>0</v>
+      <c r="H47" s="4">
+        <v>4</v>
       </c>
       <c r="I47" s="4">
         <v>10.056000000000001</v>
@@ -5568,8 +5571,8 @@
       <c r="G48" s="2">
         <v>96</v>
       </c>
-      <c r="H48" s="4" t="s">
-        <v>0</v>
+      <c r="H48" s="4">
+        <v>4</v>
       </c>
       <c r="I48" s="4">
         <v>54.633600000000001</v>
@@ -5642,8 +5645,8 @@
       <c r="G49" s="2">
         <v>108</v>
       </c>
-      <c r="H49" s="4" t="s">
-        <v>0</v>
+      <c r="H49" s="4">
+        <v>4</v>
       </c>
       <c r="I49" s="4">
         <v>33.616799999999998</v>
@@ -5716,8 +5719,8 @@
       <c r="G50" s="2">
         <v>168</v>
       </c>
-      <c r="H50" s="4" t="s">
-        <v>0</v>
+      <c r="H50" s="4">
+        <v>7</v>
       </c>
       <c r="I50" s="4">
         <v>73.77</v>
@@ -5790,8 +5793,8 @@
       <c r="G51" s="2">
         <v>204</v>
       </c>
-      <c r="H51" s="4" t="s">
-        <v>0</v>
+      <c r="H51" s="4">
+        <v>8</v>
       </c>
       <c r="I51" s="4">
         <v>20.2758</v>
@@ -5864,8 +5867,8 @@
       <c r="G52" s="2">
         <v>282</v>
       </c>
-      <c r="H52" s="4" t="s">
-        <v>0</v>
+      <c r="H52" s="4">
+        <v>11</v>
       </c>
       <c r="I52" s="4">
         <v>85.667799999999986</v>
@@ -5938,8 +5941,8 @@
       <c r="G53" s="2">
         <v>96</v>
       </c>
-      <c r="H53" s="4" t="s">
-        <v>0</v>
+      <c r="H53" s="4">
+        <v>3</v>
       </c>
       <c r="I53" s="4">
         <v>16.440000000000001</v>
@@ -6012,8 +6015,8 @@
       <c r="G54" s="2">
         <v>54</v>
       </c>
-      <c r="H54" s="4" t="s">
-        <v>0</v>
+      <c r="H54" s="4">
+        <v>2</v>
       </c>
       <c r="I54" s="4">
         <v>12.040000000000001</v>
@@ -6086,8 +6089,8 @@
       <c r="G55" s="2">
         <v>108</v>
       </c>
-      <c r="H55" s="4" t="s">
-        <v>0</v>
+      <c r="H55" s="4">
+        <v>4</v>
       </c>
       <c r="I55" s="4">
         <v>16.420999999999999</v>
@@ -6160,8 +6163,8 @@
       <c r="G56" s="2">
         <v>36</v>
       </c>
-      <c r="H56" s="4" t="s">
-        <v>0</v>
+      <c r="H56" s="4">
+        <v>2</v>
       </c>
       <c r="I56" s="4">
         <v>4.9463999999999997</v>
@@ -6234,8 +6237,8 @@
       <c r="G57" s="2">
         <v>6264</v>
       </c>
-      <c r="H57" s="4" t="s">
-        <v>0</v>
+      <c r="H57" s="4">
+        <v>285</v>
       </c>
       <c r="I57" s="4">
         <v>2690.146408333334</v>
@@ -6308,8 +6311,8 @@
       <c r="G58" s="2">
         <v>126</v>
       </c>
-      <c r="H58" s="4" t="s">
-        <v>0</v>
+      <c r="H58" s="4">
+        <v>5</v>
       </c>
       <c r="I58" s="4">
         <v>41.790599999999998</v>
@@ -6382,8 +6385,8 @@
       <c r="G59" s="2">
         <v>78</v>
       </c>
-      <c r="H59" s="4" t="s">
-        <v>0</v>
+      <c r="H59" s="4">
+        <v>3</v>
       </c>
       <c r="I59" s="4">
         <v>9.3983999999999988</v>
@@ -6456,8 +6459,8 @@
       <c r="G60" s="2">
         <v>30</v>
       </c>
-      <c r="H60" s="4" t="s">
-        <v>0</v>
+      <c r="H60" s="4">
+        <v>1</v>
       </c>
       <c r="I60" s="4">
         <v>3.3</v>
@@ -6530,8 +6533,8 @@
       <c r="G61" s="2">
         <v>54</v>
       </c>
-      <c r="H61" s="4" t="s">
-        <v>0</v>
+      <c r="H61" s="4">
+        <v>2</v>
       </c>
       <c r="I61" s="4">
         <v>6.18</v>
@@ -6604,8 +6607,8 @@
       <c r="G62" s="2">
         <v>72</v>
       </c>
-      <c r="H62" s="4" t="s">
-        <v>0</v>
+      <c r="H62" s="4">
+        <v>3</v>
       </c>
       <c r="I62" s="4">
         <v>10.129199999999999</v>
@@ -6678,8 +6681,8 @@
       <c r="G63" s="2">
         <v>24</v>
       </c>
-      <c r="H63" s="4" t="s">
-        <v>0</v>
+      <c r="H63" s="4">
+        <v>1</v>
       </c>
       <c r="I63" s="4">
         <v>13.6584</v>
@@ -6752,8 +6755,8 @@
       <c r="G64" s="2">
         <v>120</v>
       </c>
-      <c r="H64" s="4" t="s">
-        <v>0</v>
+      <c r="H64" s="4">
+        <v>4</v>
       </c>
       <c r="I64" s="4">
         <v>45.924000000000007</v>
@@ -6826,8 +6829,8 @@
       <c r="G65" s="2">
         <v>114</v>
       </c>
-      <c r="H65" s="4" t="s">
-        <v>0</v>
+      <c r="H65" s="4">
+        <v>5</v>
       </c>
       <c r="I65" s="4">
         <v>56.811599999999999</v>
@@ -6900,8 +6903,8 @@
       <c r="G66" s="2">
         <v>180</v>
       </c>
-      <c r="H66" s="4" t="s">
-        <v>0</v>
+      <c r="H66" s="4">
+        <v>6</v>
       </c>
       <c r="I66" s="4">
         <v>20.773600000000002</v>
@@ -6974,8 +6977,8 @@
       <c r="G67" s="2">
         <v>114</v>
       </c>
-      <c r="H67" s="4" t="s">
-        <v>0</v>
+      <c r="H67" s="4">
+        <v>4</v>
       </c>
       <c r="I67" s="4">
         <v>12.679200000000002</v>
@@ -7048,8 +7051,8 @@
       <c r="G68" s="2">
         <v>156</v>
       </c>
-      <c r="H68" s="4" t="s">
-        <v>0</v>
+      <c r="H68" s="4">
+        <v>6</v>
       </c>
       <c r="I68" s="4">
         <v>15.669</v>
@@ -7122,8 +7125,8 @@
       <c r="G69" s="2">
         <v>78</v>
       </c>
-      <c r="H69" s="4" t="s">
-        <v>0</v>
+      <c r="H69" s="4">
+        <v>3</v>
       </c>
       <c r="I69" s="4">
         <v>14.995200000000001</v>
@@ -7196,8 +7199,8 @@
       <c r="G70" s="2">
         <v>60</v>
       </c>
-      <c r="H70" s="4" t="s">
-        <v>0</v>
+      <c r="H70" s="4">
+        <v>2</v>
       </c>
       <c r="I70" s="4">
         <v>6.1</v>
@@ -7270,8 +7273,8 @@
       <c r="G71" s="2">
         <v>138</v>
       </c>
-      <c r="H71" s="4" t="s">
-        <v>0</v>
+      <c r="H71" s="4">
+        <v>6</v>
       </c>
       <c r="I71" s="4">
         <v>54.851199999999999</v>
@@ -7344,8 +7347,8 @@
       <c r="G72" s="2">
         <v>78</v>
       </c>
-      <c r="H72" s="4" t="s">
-        <v>0</v>
+      <c r="H72" s="4">
+        <v>3</v>
       </c>
       <c r="I72" s="4">
         <v>25.034399999999998</v>
@@ -7418,8 +7421,8 @@
       <c r="G73" s="2">
         <v>90</v>
       </c>
-      <c r="H73" s="4" t="s">
-        <v>0</v>
+      <c r="H73" s="4">
+        <v>3</v>
       </c>
       <c r="I73" s="4">
         <v>10.4</v>
@@ -7492,8 +7495,8 @@
       <c r="G74" s="2">
         <v>24</v>
       </c>
-      <c r="H74" s="4" t="s">
-        <v>0</v>
+      <c r="H74" s="4">
+        <v>1</v>
       </c>
       <c r="I74" s="4">
         <v>3.3792</v>
@@ -7566,8 +7569,8 @@
       <c r="G75" s="2">
         <v>162</v>
       </c>
-      <c r="H75" s="4" t="s">
-        <v>0</v>
+      <c r="H75" s="4">
+        <v>6</v>
       </c>
       <c r="I75" s="4">
         <v>63.854400000000005</v>
@@ -7640,8 +7643,8 @@
       <c r="G76" s="2">
         <v>24</v>
       </c>
-      <c r="H76" s="4" t="s">
-        <v>0</v>
+      <c r="H76" s="4">
+        <v>1</v>
       </c>
       <c r="I76" s="4">
         <v>3.1680000000000001</v>
@@ -7714,8 +7717,8 @@
       <c r="G77" s="2">
         <v>114</v>
       </c>
-      <c r="H77" s="4" t="s">
-        <v>0</v>
+      <c r="H77" s="4">
+        <v>4</v>
       </c>
       <c r="I77" s="4">
         <v>11.429200000000002</v>
@@ -7788,8 +7791,8 @@
       <c r="G78" s="2">
         <v>30</v>
       </c>
-      <c r="H78" s="4" t="s">
-        <v>0</v>
+      <c r="H78" s="4">
+        <v>1</v>
       </c>
       <c r="I78" s="4">
         <v>75.765599999999992</v>
@@ -7862,8 +7865,8 @@
       <c r="G79" s="2">
         <v>240</v>
       </c>
-      <c r="H79" s="4" t="s">
-        <v>0</v>
+      <c r="H79" s="4">
+        <v>10</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>150</v>
@@ -7936,8 +7939,8 @@
       <c r="G80" s="2">
         <v>318</v>
       </c>
-      <c r="H80" s="4" t="s">
-        <v>0</v>
+      <c r="H80" s="4">
+        <v>13</v>
       </c>
       <c r="I80" s="4">
         <v>155.27160000000001</v>
@@ -8010,8 +8013,8 @@
       <c r="G81" s="2">
         <v>390</v>
       </c>
-      <c r="H81" s="4" t="s">
-        <v>0</v>
+      <c r="H81" s="4">
+        <v>17</v>
       </c>
       <c r="I81" s="4">
         <v>184.74439999999998</v>
@@ -8084,8 +8087,8 @@
       <c r="G82" s="2">
         <v>294</v>
       </c>
-      <c r="H82" s="4" t="s">
-        <v>0</v>
+      <c r="H82" s="4">
+        <v>11</v>
       </c>
       <c r="I82" s="4">
         <v>149.45280000000002</v>
@@ -8158,8 +8161,8 @@
       <c r="G83" s="2">
         <v>30</v>
       </c>
-      <c r="H83" s="4" t="s">
-        <v>0</v>
+      <c r="H83" s="4">
+        <v>2</v>
       </c>
       <c r="I83" s="4">
         <v>11.154000000000002</v>
@@ -8232,8 +8235,8 @@
       <c r="G84" s="2">
         <v>246</v>
       </c>
-      <c r="H84" s="4" t="s">
-        <v>0</v>
+      <c r="H84" s="4">
+        <v>9</v>
       </c>
       <c r="I84" s="4">
         <v>57.231200000000001</v>
@@ -8306,8 +8309,8 @@
       <c r="G85" s="2">
         <v>442</v>
       </c>
-      <c r="H85" s="4" t="s">
-        <v>0</v>
+      <c r="H85" s="4">
+        <v>18</v>
       </c>
       <c r="I85" s="4">
         <v>173.3784</v>
@@ -8380,8 +8383,8 @@
       <c r="G86" s="2">
         <v>264</v>
       </c>
-      <c r="H86" s="4" t="s">
-        <v>0</v>
+      <c r="H86" s="4">
+        <v>11</v>
       </c>
       <c r="I86" s="4">
         <v>123.58320000000001</v>
@@ -8454,8 +8457,8 @@
       <c r="G87" s="2">
         <v>462</v>
       </c>
-      <c r="H87" s="4" t="s">
-        <v>0</v>
+      <c r="H87" s="4">
+        <v>19</v>
       </c>
       <c r="I87" s="4">
         <v>161.38679999999999</v>
@@ -8528,8 +8531,8 @@
       <c r="G88" s="2">
         <v>318</v>
       </c>
-      <c r="H88" s="4" t="s">
-        <v>0</v>
+      <c r="H88" s="4">
+        <v>13</v>
       </c>
       <c r="I88" s="4">
         <v>122.0232</v>
@@ -8602,8 +8605,8 @@
       <c r="G89" s="2">
         <v>318</v>
       </c>
-      <c r="H89" s="4" t="s">
-        <v>0</v>
+      <c r="H89" s="4">
+        <v>13</v>
       </c>
       <c r="I89" s="4">
         <v>145.36199999999999</v>
@@ -8676,8 +8679,8 @@
       <c r="G90" s="2">
         <v>396</v>
       </c>
-      <c r="H90" s="4" t="s">
-        <v>0</v>
+      <c r="H90" s="4">
+        <v>17</v>
       </c>
       <c r="I90" s="4">
         <v>153.1592</v>
@@ -8750,8 +8753,8 @@
       <c r="G91" s="2">
         <v>426</v>
       </c>
-      <c r="H91" s="4" t="s">
-        <v>0</v>
+      <c r="H91" s="4">
+        <v>18</v>
       </c>
       <c r="I91" s="4">
         <v>212.01599999999999</v>
@@ -8824,8 +8827,8 @@
       <c r="G92" s="2">
         <v>286</v>
       </c>
-      <c r="H92" s="4" t="s">
-        <v>0</v>
+      <c r="H92" s="4">
+        <v>12</v>
       </c>
       <c r="I92" s="4">
         <v>115.46920000000001</v>
@@ -8898,8 +8901,8 @@
       <c r="G93" s="2">
         <v>294</v>
       </c>
-      <c r="H93" s="4" t="s">
-        <v>0</v>
+      <c r="H93" s="4">
+        <v>12</v>
       </c>
       <c r="I93" s="4">
         <v>75.882000000000005</v>
@@ -8972,8 +8975,8 @@
       <c r="G94" s="2">
         <v>306</v>
       </c>
-      <c r="H94" s="4" t="s">
-        <v>0</v>
+      <c r="H94" s="4">
+        <v>13</v>
       </c>
       <c r="I94" s="4">
         <v>162.66839999999999</v>
@@ -9046,8 +9049,8 @@
       <c r="G95" s="2">
         <v>468</v>
       </c>
-      <c r="H95" s="4" t="s">
-        <v>0</v>
+      <c r="H95" s="4">
+        <v>19</v>
       </c>
       <c r="I95" s="4">
         <v>221.12880000000001</v>
@@ -9120,8 +9123,8 @@
       <c r="G96" s="2">
         <v>372</v>
       </c>
-      <c r="H96" s="4" t="s">
-        <v>0</v>
+      <c r="H96" s="4">
+        <v>15</v>
       </c>
       <c r="I96" s="4">
         <v>137.86560000000003</v>
@@ -9194,8 +9197,8 @@
       <c r="G97" s="2">
         <v>246</v>
       </c>
-      <c r="H97" s="4" t="s">
-        <v>0</v>
+      <c r="H97" s="4">
+        <v>10</v>
       </c>
       <c r="I97" s="4">
         <v>114.60720000000001</v>
@@ -9268,8 +9271,8 @@
       <c r="G98" s="2">
         <v>384</v>
       </c>
-      <c r="H98" s="4" t="s">
-        <v>0</v>
+      <c r="H98" s="4">
+        <v>15</v>
       </c>
       <c r="I98" s="4">
         <v>121.008</v>
@@ -9342,8 +9345,8 @@
       <c r="G99" s="2">
         <v>258</v>
       </c>
-      <c r="H99" s="4" t="s">
-        <v>0</v>
+      <c r="H99" s="4">
+        <v>11</v>
       </c>
       <c r="I99" s="4">
         <v>95.324400000000011</v>
@@ -9416,8 +9419,8 @@
       <c r="G100" s="2">
         <v>312</v>
       </c>
-      <c r="H100" s="4" t="s">
-        <v>0</v>
+      <c r="H100" s="4">
+        <v>13</v>
       </c>
       <c r="I100" s="4">
         <v>133.07760000000005</v>
@@ -9490,8 +9493,8 @@
       <c r="G101" s="2">
         <v>42</v>
       </c>
-      <c r="H101" s="4" t="s">
-        <v>0</v>
+      <c r="H101" s="4">
+        <v>2</v>
       </c>
       <c r="I101" s="4">
         <v>5.3244000000000007</v>
@@ -9564,8 +9567,8 @@
       <c r="G102" s="2">
         <v>510</v>
       </c>
-      <c r="H102" s="4" t="s">
-        <v>0</v>
+      <c r="H102" s="4">
+        <v>22</v>
       </c>
       <c r="I102" s="4">
         <v>249.26320000000001</v>
@@ -9638,8 +9641,8 @@
       <c r="G103" s="2">
         <v>354</v>
       </c>
-      <c r="H103" s="4" t="s">
-        <v>0</v>
+      <c r="H103" s="4">
+        <v>13</v>
       </c>
       <c r="I103" s="4">
         <v>100.7304</v>
@@ -9712,8 +9715,8 @@
       <c r="G104" s="2">
         <v>408</v>
       </c>
-      <c r="H104" s="4" t="s">
-        <v>0</v>
+      <c r="H104" s="4">
+        <v>17</v>
       </c>
       <c r="I104" s="4">
         <v>221.23439999999999</v>
@@ -9786,8 +9789,8 @@
       <c r="G105" s="2">
         <v>624</v>
       </c>
-      <c r="H105" s="4" t="s">
-        <v>0</v>
+      <c r="H105" s="4">
+        <v>27</v>
       </c>
       <c r="I105" s="4">
         <v>245.40319999999997</v>
@@ -9860,8 +9863,8 @@
       <c r="G106" s="2">
         <v>394</v>
       </c>
-      <c r="H106" s="4" t="s">
-        <v>0</v>
+      <c r="H106" s="4">
+        <v>16</v>
       </c>
       <c r="I106" s="4">
         <v>153.85360000000006</v>
@@ -9934,8 +9937,8 @@
       <c r="G107" s="2">
         <v>1279</v>
       </c>
-      <c r="H107" s="4" t="s">
-        <v>0</v>
+      <c r="H107" s="4">
+        <v>64</v>
       </c>
       <c r="I107" s="4">
         <v>574.94053333333329</v>
@@ -10008,8 +10011,8 @@
       <c r="G108" s="2">
         <v>300</v>
       </c>
-      <c r="H108" s="4" t="s">
-        <v>0</v>
+      <c r="H108" s="4">
+        <v>12</v>
       </c>
       <c r="I108" s="4">
         <v>142.22399999999999</v>
@@ -10082,8 +10085,8 @@
       <c r="G109" s="2">
         <v>438</v>
       </c>
-      <c r="H109" s="4" t="s">
-        <v>0</v>
+      <c r="H109" s="4">
+        <v>19</v>
       </c>
       <c r="I109" s="4">
         <v>193.61520000000002</v>
@@ -10156,8 +10159,8 @@
       <c r="G110" s="2">
         <v>490</v>
       </c>
-      <c r="H110" s="4" t="s">
-        <v>0</v>
+      <c r="H110" s="4">
+        <v>20</v>
       </c>
       <c r="I110" s="4">
         <v>208.10920000000002</v>
@@ -10230,8 +10233,8 @@
       <c r="G111" s="2">
         <v>144</v>
       </c>
-      <c r="H111" s="4" t="s">
-        <v>0</v>
+      <c r="H111" s="4">
+        <v>6</v>
       </c>
       <c r="I111" s="4">
         <v>81.950400000000002</v>
@@ -10304,8 +10307,8 @@
       <c r="G112" s="2">
         <v>108</v>
       </c>
-      <c r="H112" s="4" t="s">
-        <v>0</v>
+      <c r="H112" s="4">
+        <v>4</v>
       </c>
       <c r="I112" s="4">
         <v>23.204800000000002</v>
@@ -10378,8 +10381,8 @@
       <c r="G113" s="2">
         <v>144</v>
       </c>
-      <c r="H113" s="4" t="s">
-        <v>0</v>
+      <c r="H113" s="4">
+        <v>6</v>
       </c>
       <c r="I113" s="4">
         <v>28.38</v>
@@ -10452,8 +10455,8 @@
       <c r="G114" s="2">
         <v>36</v>
       </c>
-      <c r="H114" s="4" t="s">
-        <v>0</v>
+      <c r="H114" s="4">
+        <v>2</v>
       </c>
       <c r="I114" s="4">
         <v>4.9632000000000005</v>
@@ -10526,8 +10529,8 @@
       <c r="G115" s="2">
         <v>420</v>
       </c>
-      <c r="H115" s="4" t="s">
-        <v>0</v>
+      <c r="H115" s="4">
+        <v>17</v>
       </c>
       <c r="I115" s="4">
         <v>177.58680000000001</v>
